--- a/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 42,4</t>
+          <t>20,64; 42,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,35; 61,4</t>
+          <t>40,19; 61,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,97; 49,84</t>
+          <t>29,35; 49,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,05; 32,57</t>
+          <t>13,88; 32,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 46,37</t>
+          <t>23,89; 44,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,39; 57,68</t>
+          <t>36,9; 57,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 33,1</t>
+          <t>19,54; 33,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,52; 50,77</t>
+          <t>34,96; 49,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,87; 51,05</t>
+          <t>36,15; 50,11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,01</t>
+          <t>21,7; 36,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 34,61</t>
+          <t>20,17; 35,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 29,32</t>
+          <t>16,66; 28,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 34,82</t>
+          <t>21,25; 35,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 31,34</t>
+          <t>17,66; 31,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 29,18</t>
+          <t>16,11; 29,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 33,72</t>
+          <t>23,46; 33,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,99; 31,0</t>
+          <t>21,04; 31,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,05; 27,35</t>
+          <t>17,78; 27,12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,71; 47,5</t>
+          <t>26,92; 47,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 25,64</t>
+          <t>10,47; 25,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,94; 49,48</t>
+          <t>28,96; 49,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,46; 52,49</t>
+          <t>33,55; 51,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 28,15</t>
+          <t>12,18; 27,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,28; 55,77</t>
+          <t>34,83; 54,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,59</t>
+          <t>32,63; 46,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 24,59</t>
+          <t>13,68; 24,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,85; 49,63</t>
+          <t>35,39; 49,11</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 33,6</t>
+          <t>17,03; 33,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 47,43</t>
+          <t>29,52; 46,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,62; 60,7</t>
+          <t>41,75; 60,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,54; 37,48</t>
+          <t>21,08; 37,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,55; 37,47</t>
+          <t>21,83; 38,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 54,5</t>
+          <t>34,97; 55,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 32,46</t>
+          <t>20,91; 33,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,23; 39,46</t>
+          <t>27,04; 39,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,49; 54,55</t>
+          <t>41,28; 54,66</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 30,27</t>
+          <t>11,28; 30,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 32,3</t>
+          <t>10,62; 31,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 20,22</t>
+          <t>1,54; 17,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 22,65</t>
+          <t>5,98; 21,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,14; 30,49</t>
+          <t>10,09; 30,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 17,08</t>
+          <t>2,7; 15,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,14; 22,39</t>
+          <t>10,05; 22,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 27,86</t>
+          <t>12,68; 27,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 14,69</t>
+          <t>3,57; 13,71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,65; 63,12</t>
+          <t>41,75; 62,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 29,21</t>
+          <t>12,24; 30,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,18; 53,39</t>
+          <t>32,46; 53,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 44,41</t>
+          <t>25,52; 44,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 33,72</t>
+          <t>14,69; 34,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,0; 48,38</t>
+          <t>27,49; 48,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,42; 50,31</t>
+          <t>34,82; 49,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,69; 28,6</t>
+          <t>16,1; 29,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,96; 47,82</t>
+          <t>32,22; 47,95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,5; 51,15</t>
+          <t>37,58; 51,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 28,32</t>
+          <t>15,68; 27,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,27; 30,91</t>
+          <t>19,26; 32,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,29; 43,21</t>
+          <t>28,48; 42,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,57; 27,59</t>
+          <t>15,32; 27,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,85; 31,67</t>
+          <t>20,31; 32,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,05; 45,14</t>
+          <t>35,24; 45,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,18; 25,18</t>
+          <t>17,53; 25,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,08; 29,7</t>
+          <t>21,1; 29,48</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,57</t>
+          <t>14,73; 25,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,92; 31,84</t>
+          <t>21,08; 32,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 25,6</t>
+          <t>15,69; 25,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,6; 27,96</t>
+          <t>17,44; 28,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,83; 28,56</t>
+          <t>17,37; 28,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,05; 29,47</t>
+          <t>18,71; 29,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,52; 24,88</t>
+          <t>17,77; 25,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,82; 28,55</t>
+          <t>20,88; 28,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,47; 26,12</t>
+          <t>18,88; 25,56</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,17</t>
+          <t>28,75; 34,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,09; 29,57</t>
+          <t>24,47; 29,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,45; 32,11</t>
+          <t>26,39; 31,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,83; 31,49</t>
+          <t>25,89; 31,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,33; 26,42</t>
+          <t>21,24; 26,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,57; 33,49</t>
+          <t>27,66; 33,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,97; 32,08</t>
+          <t>28,14; 32,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,35; 27,35</t>
+          <t>23,44; 27,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,83; 31,77</t>
+          <t>27,68; 31,76</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14468</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28830</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22552</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30012</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26674</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>49891</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>52564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9660; 19727</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22601; 34716</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16841; 28268</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7762; 18099</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14831; 27748</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23533; 36523</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20073; 34698</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>41366; 59107</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>43798; 60701</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29015</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27636</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22692</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29704</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26550</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24127</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>58719</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>54186</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>46819</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21905; 36677</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20597; 36269</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16783; 29114</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22556; 37538</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>19172; 34290</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17555; 31646</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>48581; 69920</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>44329; 65803</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>37281; 56878</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>22720</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11881</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24954</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29192</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13387</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31096</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51913</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>25268</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>56050</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16637; 29186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7070; 17304</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18712; 31897</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22959; 35367</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8426; 19276</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23882; 37701</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>42495; 60591</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18690; 32870</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>47135; 65396</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29015</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37861</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22113</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23499</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35962</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39853</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>52514</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>73823</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>12285; 23993</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22760; 35723</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30978; 45229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16504; 29156</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17584; 30972</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>27934; 44051</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>31457; 49966</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>42635; 62378</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>63611; 84221</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8239</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>16695</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6630</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4650; 12714</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4493; 13225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>658; 7503</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2680; 9726</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4436; 13383</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1174; 6744</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8647; 19692</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>10937; 23503</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3080; 11817</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>27946</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22683</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>21196</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>47786</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>24424</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>43879</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>22526; 33744</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6510; 16021</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>17377; 28612</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14742; 25778</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8743; 20445</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>15675; 27507</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>38906; 55571</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>18147; 33650</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>35623; 53005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>55204</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29059</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>33015</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>44826</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30067</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35704</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100029</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>59126</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>68719</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>46527; 64215</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>21401; 37701</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25553; 42453</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>35844; 53894</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>21816; 38739</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>28452; 45255</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>87990; 112902</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>48892; 70911</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>57552; 80404</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>30020</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>42286</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>32675</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>35463</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38005</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>39375</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>65483</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>80291</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>72050</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>22403; 38697</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>33780; 51441</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>25177; 41006</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>27572; 44850</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>29035; 46898</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>30957; 49617</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>55137; 77950</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>68339; 93239</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>61520; 83307</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>205100</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>187911</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>199781</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>403934</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>362394</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>187669; 226564</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>170146; 207315</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>181116; 217984</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>180081; 218392</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>155737; 194490</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>201162; 240839</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>379329; 433388</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>334877; 392290</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>391273; 448977</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,64; 42,15</t>
+          <t>21,04; 41,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 61,73</t>
+          <t>40,33; 62,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 49,27</t>
+          <t>29,51; 49,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 32,36</t>
+          <t>13,21; 32,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 44,69</t>
+          <t>23,75; 43,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,9; 57,27</t>
+          <t>36,59; 57,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 33,77</t>
+          <t>19,54; 33,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,96; 49,95</t>
+          <t>35,23; 49,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,15; 50,11</t>
+          <t>36,17; 50,72</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 36,34</t>
+          <t>22,09; 36,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,17; 35,51</t>
+          <t>19,87; 34,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 28,9</t>
+          <t>16,77; 30,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 35,36</t>
+          <t>21,28; 35,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 31,59</t>
+          <t>18,01; 30,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 29,05</t>
+          <t>16,22; 29,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,46; 33,76</t>
+          <t>22,98; 33,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,04; 31,23</t>
+          <t>21,22; 31,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 27,12</t>
+          <t>17,88; 26,75</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,92; 47,23</t>
+          <t>27,34; 48,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 25,64</t>
+          <t>10,46; 26,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,96; 49,37</t>
+          <t>29,5; 49,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,55; 51,68</t>
+          <t>34,1; 52,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 27,87</t>
+          <t>12,35; 28,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,83; 54,99</t>
+          <t>35,0; 55,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,63; 46,53</t>
+          <t>32,89; 46,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,68; 24,05</t>
+          <t>13,44; 24,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,39; 49,11</t>
+          <t>34,8; 48,52</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,03; 33,26</t>
+          <t>17,45; 33,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,52; 46,33</t>
+          <t>29,53; 47,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,75; 60,95</t>
+          <t>40,98; 60,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,08; 37,24</t>
+          <t>21,18; 37,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,83; 38,44</t>
+          <t>21,18; 37,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,97; 55,15</t>
+          <t>35,71; 54,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 33,21</t>
+          <t>20,59; 32,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,04; 39,56</t>
+          <t>27,93; 39,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,28; 54,66</t>
+          <t>40,61; 53,94</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 30,84</t>
+          <t>9,81; 31,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 31,27</t>
+          <t>10,87; 33,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 17,55</t>
+          <t>2,48; 18,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 21,69</t>
+          <t>6,07; 22,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 30,43</t>
+          <t>10,16; 31,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,53</t>
+          <t>2,64; 16,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 22,88</t>
+          <t>10,13; 23,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 27,24</t>
+          <t>13,05; 27,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 13,71</t>
+          <t>3,53; 13,51</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,75; 62,54</t>
+          <t>40,42; 62,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 30,13</t>
+          <t>12,43; 30,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,46; 53,45</t>
+          <t>30,72; 52,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,52; 44,62</t>
+          <t>24,1; 43,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,69; 34,34</t>
+          <t>14,8; 33,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,49; 48,24</t>
+          <t>26,08; 47,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,82; 49,74</t>
+          <t>35,68; 50,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,1; 29,85</t>
+          <t>15,4; 28,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,22; 47,95</t>
+          <t>32,03; 48,17</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,58; 51,86</t>
+          <t>37,34; 52,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 27,62</t>
+          <t>15,79; 27,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,26; 32,0</t>
+          <t>18,51; 31,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,48; 42,81</t>
+          <t>28,55; 43,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,32; 27,2</t>
+          <t>15,98; 27,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,31; 32,31</t>
+          <t>20,18; 31,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,24; 45,22</t>
+          <t>35,29; 44,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,53; 25,42</t>
+          <t>17,1; 25,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,1; 29,48</t>
+          <t>20,93; 29,85</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,73; 25,44</t>
+          <t>14,74; 25,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 32,1</t>
+          <t>21,32; 32,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,69; 25,56</t>
+          <t>15,62; 26,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,44; 28,37</t>
+          <t>17,36; 28,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,37; 28,06</t>
+          <t>17,57; 28,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,71; 29,99</t>
+          <t>18,98; 30,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,77; 25,13</t>
+          <t>17,23; 24,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 28,48</t>
+          <t>21,08; 28,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,88; 25,56</t>
+          <t>18,26; 26,02</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,75; 34,71</t>
+          <t>28,54; 34,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,82</t>
+          <t>24,12; 29,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,76</t>
+          <t>26,51; 31,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,89; 31,4</t>
+          <t>25,99; 31,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,24; 26,52</t>
+          <t>21,2; 26,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,66; 33,12</t>
+          <t>27,26; 33,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,14; 32,15</t>
+          <t>28,15; 32,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,44; 27,46</t>
+          <t>23,61; 27,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,76</t>
+          <t>27,66; 31,72</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9660; 19727</t>
+          <t>9847; 19630</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22601; 34716</t>
+          <t>22682; 35173</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16841; 28268</t>
+          <t>16929; 28586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7762; 18099</t>
+          <t>7391; 17923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14831; 27748</t>
+          <t>14745; 27159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23533; 36523</t>
+          <t>23331; 36743</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20073; 34698</t>
+          <t>20076; 34139</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41366; 59107</t>
+          <t>41679; 59016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43798; 60701</t>
+          <t>43819; 61438</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21905; 36677</t>
+          <t>22296; 37035</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20597; 36269</t>
+          <t>20297; 35601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16783; 29114</t>
+          <t>16896; 30638</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22556; 37538</t>
+          <t>22589; 37593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19172; 34290</t>
+          <t>19551; 33390</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17555; 31646</t>
+          <t>17668; 31821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48581; 69920</t>
+          <t>47587; 68518</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44329; 65803</t>
+          <t>44714; 65551</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37281; 56878</t>
+          <t>37487; 56092</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16637; 29186</t>
+          <t>16893; 30156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7070; 17304</t>
+          <t>7061; 17722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18712; 31897</t>
+          <t>19060; 31898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22959; 35367</t>
+          <t>23332; 36059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8426; 19276</t>
+          <t>8542; 19867</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23882; 37701</t>
+          <t>23996; 37749</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42495; 60591</t>
+          <t>42832; 60870</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18690; 32870</t>
+          <t>18371; 32946</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47135; 65396</t>
+          <t>46339; 64619</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12285; 23993</t>
+          <t>12585; 24390</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22760; 35723</t>
+          <t>22769; 36403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30978; 45229</t>
+          <t>30405; 44535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16504; 29156</t>
+          <t>16586; 29219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17584; 30972</t>
+          <t>17064; 30605</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27934; 44051</t>
+          <t>28521; 43425</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31457; 49966</t>
+          <t>30968; 49092</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42635; 62378</t>
+          <t>44033; 62922</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63611; 84221</t>
+          <t>62572; 83105</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4650; 12714</t>
+          <t>4045; 12784</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4493; 13225</t>
+          <t>4599; 14098</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>658; 7503</t>
+          <t>1059; 8089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2680; 9726</t>
+          <t>2721; 10091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4436; 13383</t>
+          <t>4468; 13754</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1174; 6744</t>
+          <t>1146; 7318</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8647; 19692</t>
+          <t>8722; 19850</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10937; 23503</t>
+          <t>11258; 23762</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3080; 11817</t>
+          <t>3045; 11645</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22526; 33744</t>
+          <t>21808; 33544</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6510; 16021</t>
+          <t>6612; 15953</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17377; 28612</t>
+          <t>16445; 28248</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14742; 25778</t>
+          <t>13920; 24901</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8743; 20445</t>
+          <t>8808; 19786</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15675; 27507</t>
+          <t>14873; 27258</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38906; 55571</t>
+          <t>39862; 56052</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18147; 33650</t>
+          <t>17359; 32294</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35623; 53005</t>
+          <t>35406; 53256</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46527; 64215</t>
+          <t>46233; 64520</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21401; 37701</t>
+          <t>21553; 38108</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25553; 42453</t>
+          <t>24563; 42169</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35844; 53894</t>
+          <t>35935; 54467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21816; 38739</t>
+          <t>22760; 39660</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28452; 45255</t>
+          <t>28264; 44389</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87990; 112902</t>
+          <t>88125; 112320</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48892; 70911</t>
+          <t>47705; 70924</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>57552; 80404</t>
+          <t>57081; 81424</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22403; 38697</t>
+          <t>22417; 38093</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>33780; 51441</t>
+          <t>34170; 52522</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25177; 41006</t>
+          <t>25056; 42021</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27572; 44850</t>
+          <t>27443; 44542</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29035; 46898</t>
+          <t>29361; 47018</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30957; 49617</t>
+          <t>31398; 50156</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>55137; 77950</t>
+          <t>53450; 77098</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>68339; 93239</t>
+          <t>69022; 94679</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61520; 83307</t>
+          <t>59515; 84815</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>187669; 226564</t>
+          <t>186301; 225741</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>170146; 207315</t>
+          <t>167710; 207091</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>181116; 217984</t>
+          <t>181939; 218783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180081; 218392</t>
+          <t>180744; 218650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>155737; 194490</t>
+          <t>155443; 193585</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>201162; 240839</t>
+          <t>198247; 240145</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>379329; 433388</t>
+          <t>379490; 432192</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>334877; 392290</t>
+          <t>337279; 388911</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>391273; 448977</t>
+          <t>390945; 448340</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>30,91%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>51,26%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39,31%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,04; 41,94</t>
+          <t>14,05; 32,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,33; 62,54</t>
+          <t>24,5; 46,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,51; 49,83</t>
+          <t>37,39; 57,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 32,04</t>
+          <t>21,69; 42,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,75; 43,75</t>
+          <t>40,35; 61,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,59; 57,62</t>
+          <t>29,97; 49,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 33,23</t>
+          <t>19,64; 33,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,23; 49,88</t>
+          <t>35,52; 50,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,17; 50,72</t>
+          <t>35,87; 51,05</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>28,75%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>27,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,52%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 36,7</t>
+          <t>21,7; 34,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,87; 34,86</t>
+          <t>17,99; 31,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 30,41</t>
+          <t>16,31; 29,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,28; 35,41</t>
+          <t>21,89; 36,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 30,76</t>
+          <t>20,36; 34,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 29,21</t>
+          <t>17,06; 29,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98; 33,09</t>
+          <t>23,26; 33,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,22; 31,11</t>
+          <t>20,99; 31,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 26,75</t>
+          <t>18,05; 27,35</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42,66%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>36,77%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,6%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38,62%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42,66%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,34; 48,8</t>
+          <t>33,46; 52,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,46; 26,25</t>
+          <t>11,87; 28,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,5; 49,37</t>
+          <t>35,28; 55,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,1; 52,69</t>
+          <t>27,71; 47,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 28,73</t>
+          <t>10,34; 25,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,0; 55,06</t>
+          <t>27,94; 49,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,89; 46,74</t>
+          <t>33,45; 46,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,44; 24,11</t>
+          <t>13,91; 24,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,8; 48,52</t>
+          <t>34,85; 49,63</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>24,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>37,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 33,81</t>
+          <t>20,54; 37,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,53; 47,21</t>
+          <t>20,55; 37,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,98; 60,02</t>
+          <t>35,44; 54,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 37,32</t>
+          <t>17,28; 33,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 37,99</t>
+          <t>29,2; 47,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,71; 54,36</t>
+          <t>42,62; 60,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 32,63</t>
+          <t>21,09; 32,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 39,91</t>
+          <t>27,23; 39,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,61; 53,94</t>
+          <t>40,49; 54,55</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,74%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>19,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,84%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 31,01</t>
+          <t>5,97; 22,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 33,33</t>
+          <t>10,14; 30,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 18,92</t>
+          <t>2,71; 17,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 22,5</t>
+          <t>11,04; 30,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 31,28</t>
+          <t>10,47; 32,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 16,85</t>
+          <t>2,58; 20,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,13; 23,06</t>
+          <t>10,14; 22,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 27,54</t>
+          <t>12,88; 27,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,51</t>
+          <t>3,89; 14,69</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34,34%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,97%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>51,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34,34%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,42; 62,17</t>
+          <t>25,26; 44,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,43; 30,0</t>
+          <t>14,09; 33,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 52,77</t>
+          <t>27,0; 48,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,1; 43,1</t>
+          <t>41,65; 63,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,8; 33,24</t>
+          <t>11,46; 29,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,08; 47,8</t>
+          <t>31,18; 53,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,68; 50,17</t>
+          <t>35,42; 50,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,4; 28,65</t>
+          <t>15,69; 28,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,03; 48,17</t>
+          <t>31,96; 47,82</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35,61%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>44,59%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>21,29%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>24,88%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35,61%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,34; 52,11</t>
+          <t>29,29; 43,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,79; 27,92</t>
+          <t>15,57; 27,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,51; 31,78</t>
+          <t>19,85; 31,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,55; 43,27</t>
+          <t>37,5; 51,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,98; 27,85</t>
+          <t>16,09; 28,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,18; 31,69</t>
+          <t>18,27; 30,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,29; 44,98</t>
+          <t>35,05; 45,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,1; 25,43</t>
+          <t>17,18; 25,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,93; 29,85</t>
+          <t>21,08; 29,7</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>19,74%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>26,39%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>20,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,04</t>
+          <t>17,6; 27,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,32; 32,78</t>
+          <t>17,83; 28,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,62; 26,19</t>
+          <t>19,05; 29,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,36; 28,17</t>
+          <t>14,99; 25,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,57; 28,13</t>
+          <t>20,92; 31,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,98; 30,31</t>
+          <t>15,89; 25,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,23; 24,85</t>
+          <t>17,52; 24,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 28,92</t>
+          <t>20,82; 28,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,26; 26,02</t>
+          <t>18,47; 26,12</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,58</t>
+          <t>25,83; 31,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,12; 29,79</t>
+          <t>21,33; 26,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,51; 31,88</t>
+          <t>27,57; 33,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,99; 31,44</t>
+          <t>28,5; 34,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,2; 26,4</t>
+          <t>24,09; 29,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,26; 33,03</t>
+          <t>26,45; 32,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,15; 32,06</t>
+          <t>27,97; 32,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,61; 27,22</t>
+          <t>23,35; 27,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,66; 31,72</t>
+          <t>27,83; 31,77</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12206</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21061</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30012</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>14468</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>28830</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>22552</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21061</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30012</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9847; 19630</t>
+          <t>7860; 18222</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22682; 35173</t>
+          <t>15210; 28789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16929; 28586</t>
+          <t>23846; 36781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7391; 17923</t>
+          <t>10150; 19846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14745; 27159</t>
+          <t>22689; 34530</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23331; 36743</t>
+          <t>17195; 28593</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20076; 34139</t>
+          <t>20177; 34013</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41679; 59016</t>
+          <t>42024; 60076</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43819; 61438</t>
+          <t>43454; 61843</t>
         </is>
       </c>
     </row>
@@ -1923,27 +1923,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26550</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24127</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>29015</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>27636</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22692</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29704</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26550</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24127</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22296; 37035</t>
+          <t>23036; 36973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20297; 35601</t>
+          <t>19523; 34012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16896; 30638</t>
+          <t>17770; 31793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22589; 37593</t>
+          <t>22089; 36347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19551; 33390</t>
+          <t>20795; 35354</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17668; 31821</t>
+          <t>17187; 29537</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47587; 68518</t>
+          <t>48171; 69834</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44714; 65551</t>
+          <t>44224; 65316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37487; 56092</t>
+          <t>37858; 57360</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29192</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13387</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31096</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>22720</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>11881</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>24954</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29192</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13387</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31096</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16893; 30156</t>
+          <t>22896; 35923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7061; 17722</t>
+          <t>8209; 19469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19060; 31898</t>
+          <t>24190; 38240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23332; 36059</t>
+          <t>17122; 29353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8542; 19867</t>
+          <t>6977; 17305</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23996; 37749</t>
+          <t>18049; 31970</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42832; 60870</t>
+          <t>43565; 60667</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18371; 32946</t>
+          <t>19013; 33600</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46339; 64619</t>
+          <t>46418; 66098</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22113</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23499</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35962</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>17740</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>29015</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>37861</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22113</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23499</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35962</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12585; 24390</t>
+          <t>16079; 29349</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22769; 36403</t>
+          <t>16555; 30190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30405; 44535</t>
+          <t>28308; 43536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16586; 29219</t>
+          <t>12466; 24234</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17064; 30605</t>
+          <t>22520; 36577</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28521; 43425</t>
+          <t>31627; 45038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30968; 49092</t>
+          <t>31731; 48831</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44033; 62922</t>
+          <t>42942; 62220</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62572; 83105</t>
+          <t>62390; 84051</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5489</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8239</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>7988</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8456</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3350</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5489</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8239</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3280</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4045; 12784</t>
+          <t>2676; 10156</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4599; 14098</t>
+          <t>4458; 13409</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1059; 8089</t>
+          <t>1176; 7418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2721; 10091</t>
+          <t>4553; 12482</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4468; 13754</t>
+          <t>4430; 13661</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1146; 7318</t>
+          <t>1103; 8642</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8722; 19850</t>
+          <t>8728; 19273</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11258; 23762</t>
+          <t>11114; 24032</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3045; 11645</t>
+          <t>3349; 12663</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19841</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21196</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>27946</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>10749</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>22683</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19841</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>13676</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>21196</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21808; 33544</t>
+          <t>14595; 25656</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6612; 15953</t>
+          <t>8387; 20075</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16445; 28248</t>
+          <t>15395; 27590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13920; 24901</t>
+          <t>22471; 34057</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8808; 19786</t>
+          <t>6097; 15533</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14873; 27258</t>
+          <t>16688; 28579</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39862; 56052</t>
+          <t>39567; 56206</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17359; 32294</t>
+          <t>17687; 32237</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35406; 53256</t>
+          <t>35327; 52860</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>44826</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>30067</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>35704</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>55204</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>29059</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>33015</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>44826</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>30067</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35704</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46233; 64520</t>
+          <t>36869; 54388</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21553; 38108</t>
+          <t>22171; 39290</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24563; 42169</t>
+          <t>27807; 44365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35935; 54467</t>
+          <t>46430; 63333</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22760; 39660</t>
+          <t>21967; 38655</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28264; 44389</t>
+          <t>24238; 41016</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88125; 112320</t>
+          <t>87511; 112706</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47705; 70924</t>
+          <t>47913; 70228</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>57081; 81424</t>
+          <t>57493; 81012</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>35463</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>38005</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>39375</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>30020</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>42286</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>32675</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>35463</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>38005</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>39375</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22417; 38093</t>
+          <t>27828; 44210</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34170; 52522</t>
+          <t>29802; 47728</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25056; 42021</t>
+          <t>31522; 48768</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27443; 44542</t>
+          <t>22801; 38891</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29361; 47018</t>
+          <t>33515; 51016</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31398; 50156</t>
+          <t>25500; 41071</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53450; 77098</t>
+          <t>54338; 77173</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>69022; 94679</t>
+          <t>68161; 93450</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>59515; 84815</t>
+          <t>60204; 85139</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>269</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>301</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>199781</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>198834</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>174484</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>186301; 225741</t>
+          <t>179601; 218963</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>167710; 207091</t>
+          <t>156425; 193734</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>181939; 218783</t>
+          <t>200495; 243531</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180744; 218650</t>
+          <t>186056; 223047</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>155443; 193585</t>
+          <t>167451; 205543</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>198247; 240145</t>
+          <t>181532; 220370</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>379490; 432192</t>
+          <t>377129; 432518</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>337279; 388911</t>
+          <t>333567; 390742</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>390945; 448340</t>
+          <t>393370; 449071</t>
         </is>
       </c>
     </row>
